--- a/interview_forms/046_customer_support_interview_form--interview_forms.xlsx
+++ b/interview_forms/046_customer_support_interview_form--interview_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -968,8 +968,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -997,12 +997,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School', 'value': 'high_school'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'some_college',_'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Some College', 'value': 'some_college'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bachelors',_'value':_'bachelors'}</t>
+          <t>bachelors</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bachelors', 'value': 'bachelors'}</t>
+          <t>Bachelors</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'masters',_'value':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Masters', 'value': 'masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'phd',_'value':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'PhD', 'value': 'phd'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'communication',_'value':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Communication', 'value': 'communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'problem_solving',_'value':_'problem_solving'}</t>
+          <t>problem_solving</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Problem Solving', 'value': 'problem_solving'}</t>
+          <t>Problem Solving</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'time_management',_'value':_'time_management'}</t>
+          <t>time_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Time Management', 'value': 'time_management'}</t>
+          <t>Time Management</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'team_management',_'value':_'team_management'}</t>
+          <t>team_management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Team Management', 'value': 'team_management'}</t>
+          <t>Team Management</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'leadership',_'value':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Leadership', 'value': 'leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'first_aid',_'value':_'first_aid'}</t>
+          <t>first_aid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'First Aid', 'value': 'first_aid'}</t>
+          <t>First Aid</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'basic_life_support',_'value':_'basic_life_support'}</t>
+          <t>basic_life_support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Basic Life Support', 'value': 'basic_life_support'}</t>
+          <t>Basic Life Support</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'crisis_management',_'value':_'crisis_management'}</t>
+          <t>crisis_management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Crisis Management', 'value': 'crisis_management'}</t>
+          <t>Crisis Management</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'data_analysis',_'value':_'data_analysis'}</t>
+          <t>data_analysis</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Data Analysis', 'value': 'data_analysis'}</t>
+          <t>Data Analysis</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday', 'value': 'monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday', 'value': 'tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday', 'value': 'wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday', 'value': 'thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday', 'value': 'friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday', 'value': 'saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday', 'value': 'sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'in-person',_'value':_'in_person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'In-person', 'value': 'in_person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'video_call',_'value':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Video call', 'value': 'video_call'}</t>
+          <t>Video call</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English', 'value': 'english'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish', 'value': 'spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'french',_'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'French', 'value': 'french'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'german',_'value':_'german'}</t>
+          <t>german</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'German', 'value': 'german'}</t>
+          <t>German</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'currently_working',_'value':_'currently_working'}</t>
+          <t>currently_working</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Currently Working', 'value': 'currently_working'}</t>
+          <t>Currently Working</t>
         </is>
       </c>
     </row>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'formerly_working',_'value':_'formerly_working'}</t>
+          <t>formerly_working</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Formerly Working', 'value': 'formerly_working'}</t>
+          <t>Formerly Working</t>
         </is>
       </c>
     </row>
@@ -1575,12 +1575,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_employed',_'value':_'not_employed'}</t>
+          <t>not_employed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Employed', 'value': 'not_employed'}</t>
+          <t>Not Employed</t>
         </is>
       </c>
     </row>
